--- a/surface_inventory_updated.xlsx
+++ b/surface_inventory_updated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOB\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KevinO'Bryan\Downloads\Job-Specific-AI-Agents-Slides-and-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3876579-9077-4553-BCBE-760BD93D5DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9581801D-EA32-4D69-854F-84F08EAC03ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="315" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Device Name</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>Surface Pro 7</t>
+  </si>
+  <si>
+    <t>Assigned Count</t>
   </si>
 </sst>
 </file>
@@ -475,18 +478,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,8 +509,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -525,8 +532,11 @@
       <c r="F2">
         <v>5</v>
       </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -545,8 +555,11 @@
       <c r="F3">
         <v>3</v>
       </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -565,8 +578,11 @@
       <c r="F4">
         <v>2</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -585,8 +601,11 @@
       <c r="F5">
         <v>6</v>
       </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -605,8 +624,11 @@
       <c r="F6">
         <v>4</v>
       </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -623,6 +645,9 @@
         <v>15</v>
       </c>
       <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
         <v>3</v>
       </c>
     </row>
